--- a/artfynd/A 6189-2026 artfynd.xlsx
+++ b/artfynd/A 6189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103690137</v>
+        <v>103690140</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382979.2075467319</v>
+        <v>382993</v>
       </c>
       <c r="R2" t="n">
-        <v>6780772.422212442</v>
+        <v>6780705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>103690138</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382979.2075467319</v>
+        <v>382979</v>
       </c>
       <c r="R3" t="n">
-        <v>6780772.422212442</v>
+        <v>6780772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103690139</v>
+        <v>103690136</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382979.2075467319</v>
+        <v>383146</v>
       </c>
       <c r="R4" t="n">
-        <v>6780772.422212442</v>
+        <v>6780796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103690140</v>
+        <v>103690139</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>382992.9158378693</v>
+        <v>382979</v>
       </c>
       <c r="R5" t="n">
-        <v>6780704.310877055</v>
+        <v>6780772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106381612</v>
+        <v>106381608</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>382991.6613619444</v>
+        <v>383098</v>
       </c>
       <c r="R6" t="n">
-        <v>6780797.620373375</v>
+        <v>6780781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106381613</v>
+        <v>106381609</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>382979.9477800531</v>
+        <v>383042</v>
       </c>
       <c r="R7" t="n">
-        <v>6780780.129596268</v>
+        <v>6780749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106381616</v>
+        <v>106381610</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>382987.3163690448</v>
+        <v>383043</v>
       </c>
       <c r="R8" t="n">
-        <v>6780754.2723556</v>
+        <v>6780773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106381617</v>
+        <v>106381611</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>382988.4221709192</v>
+        <v>383046</v>
       </c>
       <c r="R9" t="n">
-        <v>6780685.613087098</v>
+        <v>6780788</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106381608</v>
+        <v>106381612</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>383098.0756048485</v>
+        <v>382992</v>
       </c>
       <c r="R10" t="n">
-        <v>6780781.037010741</v>
+        <v>6780798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106381614</v>
+        <v>106381613</v>
       </c>
       <c r="B11" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>382971.327521108</v>
+        <v>382980</v>
       </c>
       <c r="R11" t="n">
-        <v>6780768.334932806</v>
+        <v>6780780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106381610</v>
+        <v>106381616</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>383043.1223981464</v>
+        <v>382987</v>
       </c>
       <c r="R12" t="n">
-        <v>6780773.1974931</v>
+        <v>6780754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106381611</v>
+        <v>106381614</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>383046.036958956</v>
+        <v>382971</v>
       </c>
       <c r="R13" t="n">
-        <v>6780788.081350093</v>
+        <v>6780768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,50 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106381609</v>
+        <v>103690137</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rörbäcksnäs med omnejd, Dlr</t>
+          <t>Storheden V, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>383042.3204585626</v>
+        <v>382979</v>
       </c>
       <c r="R14" t="n">
-        <v>6780749.061592357</v>
+        <v>6780772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,22 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,6 +1933,103 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106381617</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rörbäcksnäs med omnejd, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>382988</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6780686</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6189-2026 artfynd.xlsx
+++ b/artfynd/A 6189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690139</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381608</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381609</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381610</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381611</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381612</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381613</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381616</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381614</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,8 +2100,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106381617</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>